--- a/data/trans_dic/IP19C02-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP19C02-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que en su última visita al dentista fue por limpieza de boca</t>
+          <t>Menores que en su última visita al dentista fue por limpieza de boca (tasa de respuesta: 99,44%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,8; 11,94</t>
+          <t>2,75; 12,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,86; 11,37</t>
+          <t>1,88; 11,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,78; 25,78</t>
+          <t>9,87; 25,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21,57; 40,06</t>
+          <t>22,09; 39,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,97; 8,78</t>
+          <t>1,59; 9,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,85; 10,75</t>
+          <t>1,77; 10,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,54; 31,49</t>
+          <t>14,67; 31,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17,64; 40,47</t>
+          <t>15,44; 39,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,84; 9,23</t>
+          <t>2,64; 8,8</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,71; 9,03</t>
+          <t>2,74; 9,4</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14,01; 25,67</t>
+          <t>14,72; 26,24</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>21,54; 37,45</t>
+          <t>22,0; 36,47</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,61; 12,89</t>
+          <t>4,76; 12,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,71; 7,94</t>
+          <t>1,65; 7,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,03; 26,24</t>
+          <t>14,61; 26,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27,83; 42,73</t>
+          <t>28,77; 43,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,23; 12,64</t>
+          <t>4,22; 12,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,45; 11,36</t>
+          <t>3,36; 11,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,48; 25,97</t>
+          <t>13,62; 26,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>35,81; 49,83</t>
+          <t>35,63; 49,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,34; 10,93</t>
+          <t>5,64; 11,13</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,13; 7,91</t>
+          <t>3,18; 7,88</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15,63; 24,28</t>
+          <t>15,39; 24,37</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>34,91; 45,27</t>
+          <t>34,54; 45,47</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,71; 11,52</t>
+          <t>2,96; 12,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,44; 11,71</t>
+          <t>2,17; 11,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,94; 24,67</t>
+          <t>10,93; 24,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,33; 29,09</t>
+          <t>13,85; 29,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,73; 12,53</t>
+          <t>3,58; 12,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,76; 7,66</t>
+          <t>0,76; 7,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,84; 29,34</t>
+          <t>13,95; 29,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,09; 31,56</t>
+          <t>13,42; 31,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,17; 10,14</t>
+          <t>4,11; 10,49</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,17; 7,84</t>
+          <t>2,18; 7,83</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14,37; 24,68</t>
+          <t>14,42; 24,28</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,88; 27,34</t>
+          <t>15,39; 27,03</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,89; 13,27</t>
+          <t>3,74; 13,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,04; 14,86</t>
+          <t>4,15; 14,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,77; 28,07</t>
+          <t>14,66; 28,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25,51; 41,3</t>
+          <t>24,41; 40,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,55; 12,94</t>
+          <t>3,09; 12,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,5; 16,65</t>
+          <t>5,47; 16,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,49; 23,66</t>
+          <t>11,12; 22,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>21,22; 37,4</t>
+          <t>21,9; 37,22</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,72; 11,25</t>
+          <t>4,62; 10,94</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,11; 13,32</t>
+          <t>6,09; 13,59</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14,32; 23,34</t>
+          <t>14,29; 23,4</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>25,4; 36,63</t>
+          <t>25,28; 36,4</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,47; 9,96</t>
+          <t>5,2; 9,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,02; 8,09</t>
+          <t>3,9; 8,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,77; 22,53</t>
+          <t>15,74; 22,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25,58; 33,85</t>
+          <t>25,63; 34,09</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,79; 9,18</t>
+          <t>4,89; 9,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,56; 8,85</t>
+          <t>4,61; 8,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,92; 23,03</t>
+          <t>16,14; 23,27</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>27,22; 35,7</t>
+          <t>27,38; 35,86</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,61; 8,89</t>
+          <t>5,53; 8,65</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,69; 7,74</t>
+          <t>4,76; 7,81</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16,83; 21,65</t>
+          <t>16,97; 21,77</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>27,74; 33,94</t>
+          <t>27,7; 33,7</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que en su última visita al dentista fue por limpieza de boca (tasa de respuesta: 99,44%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>4876</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3744</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>11725</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>21148</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>3551</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>3960</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>16655</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>24369</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>8427</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>7704</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>28380</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>45518</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2079; 9537</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1388; 8411</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>6994; 17970</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>15411; 27684</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1310; 7909</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1332; 7714</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>11120; 23692</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>13160; 33275</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>4173; 13893</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>4094; 14022</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>21590; 38481</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>34098; 56537</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>9011</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4511</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>21373</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>40532</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>8747</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>7241</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>21295</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>71298</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>17758</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>11752</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>42668</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>111830</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>5236; 14243</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1845; 8371</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>15659; 28362</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>32726; 49481</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>4713; 14217</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>3858; 12721</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>14792; 28586</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>59631; 82890</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>12501; 24668</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>7203; 17855</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>33198; 52581</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>97098; 127832</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>4418</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4443</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>13026</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>21415</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>5626</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2184</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>16200</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>24783</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>10045</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>6627</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>29225</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>46198</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2048; 8848</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1618; 8212</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>8264; 18745</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>14814; 31105</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2786; 9871</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>609; 5738</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>10721; 22897</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>16134; 37918</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>6049; 15434</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>3363; 12071</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>21990; 37022</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>34964; 61411</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>7436</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>7663</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>22654</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>33244</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>6217</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>9827</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>17789</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>32059</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>13653</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>17490</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>40443</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>65304</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>3588; 12711</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>3854; 13180</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>15979; 30691</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>24696; 41414</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>2780; 10947</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>5263; 15686</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>11874; 24347</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>24435; 41531</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>8591; 20349</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>11525; 25716</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>30839; 50479</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>53781; 77446</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>25741</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>20361</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>68778</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>116339</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>24141</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>23211</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>71938</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>152510</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>49882</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>43572</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>140716</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>268849</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>18261; 33783</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>13779; 28946</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>57080; 82128</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>100387; 133507</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>17678; 32695</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>16876; 32379</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>59392; 85650</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>132619; 173719</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>39392; 61615</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>34252; 56189</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>123958; 159082</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>242682; 295243</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP19C02-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP19C02-Habitat-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,75; 12,6</t>
+          <t>2,73; 12,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,88; 11,38</t>
+          <t>1,92; 11,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,87; 25,37</t>
+          <t>9,92; 24,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22,09; 39,68</t>
+          <t>21,66; 39,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,59; 9,62</t>
+          <t>1,59; 8,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,77; 10,25</t>
+          <t>1,79; 11,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,67; 31,26</t>
+          <t>14,29; 31,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,44; 39,03</t>
+          <t>16,76; 39,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,64; 8,8</t>
+          <t>2,96; 8,66</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,74; 9,4</t>
+          <t>2,65; 8,98</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14,72; 26,24</t>
+          <t>14,6; 25,52</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>22,0; 36,47</t>
+          <t>21,76; 36,1</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,76; 12,94</t>
+          <t>4,66; 12,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,65; 7,48</t>
+          <t>1,72; 7,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,61; 26,46</t>
+          <t>13,8; 25,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28,77; 43,51</t>
+          <t>28,18; 43,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,22; 12,74</t>
+          <t>4,25; 12,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,36; 11,09</t>
+          <t>3,41; 11,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,62; 26,32</t>
+          <t>13,64; 25,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>35,63; 49,52</t>
+          <t>36,08; 49,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,64; 11,13</t>
+          <t>5,32; 11,29</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,18; 7,88</t>
+          <t>2,94; 7,79</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15,39; 24,37</t>
+          <t>15,62; 24,53</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>34,54; 45,47</t>
+          <t>34,97; 44,98</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,96; 12,78</t>
+          <t>2,97; 12,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,17; 11,02</t>
+          <t>2,76; 12,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,93; 24,8</t>
+          <t>11,53; 24,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,85; 29,08</t>
+          <t>12,7; 28,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,58; 12,68</t>
+          <t>3,48; 13,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,76; 7,19</t>
+          <t>0,76; 8,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,95; 29,79</t>
+          <t>13,21; 29,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,42; 31,53</t>
+          <t>12,99; 31,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,11; 10,49</t>
+          <t>4,2; 10,88</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,18; 7,83</t>
+          <t>1,98; 7,49</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14,42; 24,28</t>
+          <t>14,61; 24,81</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,39; 27,03</t>
+          <t>15,17; 27,03</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,74; 13,24</t>
+          <t>3,98; 13,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,15; 14,18</t>
+          <t>4,09; 14,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,66; 28,15</t>
+          <t>14,82; 28,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24,41; 40,93</t>
+          <t>24,89; 40,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,09; 12,16</t>
+          <t>3,1; 11,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,47; 16,29</t>
+          <t>5,79; 17,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,12; 22,81</t>
+          <t>11,07; 23,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>21,9; 37,22</t>
+          <t>21,79; 37,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,62; 10,94</t>
+          <t>4,67; 11,23</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,09; 13,59</t>
+          <t>6,16; 13,22</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14,29; 23,4</t>
+          <t>14,96; 23,78</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>25,28; 36,4</t>
+          <t>25,21; 36,75</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,2; 9,63</t>
+          <t>5,27; 9,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,9; 8,19</t>
+          <t>3,92; 7,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,74; 22,65</t>
+          <t>15,68; 22,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25,63; 34,09</t>
+          <t>25,56; 33,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,89; 9,04</t>
+          <t>4,79; 9,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,61; 8,85</t>
+          <t>4,56; 8,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,14; 23,27</t>
+          <t>16,33; 23,38</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>27,38; 35,86</t>
+          <t>27,2; 35,82</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,53; 8,65</t>
+          <t>5,59; 8,53</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,76; 7,81</t>
+          <t>4,8; 7,49</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16,97; 21,77</t>
+          <t>17,07; 21,7</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>27,7; 33,7</t>
+          <t>27,75; 33,78</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2079; 9537</t>
+          <t>2065; 9313</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1388; 8411</t>
+          <t>1422; 8847</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6994; 17970</t>
+          <t>7030; 17498</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15411; 27684</t>
+          <t>15114; 27819</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1310; 7909</t>
+          <t>1303; 7377</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1332; 7714</t>
+          <t>1347; 8698</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11120; 23692</t>
+          <t>10833; 23644</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13160; 33275</t>
+          <t>14292; 33246</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4173; 13893</t>
+          <t>4677; 13678</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4094; 14022</t>
+          <t>3950; 13389</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21590; 38481</t>
+          <t>21409; 37425</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>34098; 56537</t>
+          <t>33735; 55965</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5236; 14243</t>
+          <t>5128; 14225</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1845; 8371</t>
+          <t>1923; 8691</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15659; 28362</t>
+          <t>14790; 27719</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>32726; 49481</t>
+          <t>32045; 49887</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4713; 14217</t>
+          <t>4740; 14126</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3858; 12721</t>
+          <t>3910; 12668</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14792; 28586</t>
+          <t>14815; 28151</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>59631; 82890</t>
+          <t>60383; 82659</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12501; 24668</t>
+          <t>11786; 25036</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7203; 17855</t>
+          <t>6666; 17638</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33198; 52581</t>
+          <t>33695; 52919</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>97098; 127832</t>
+          <t>98310; 126437</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2048; 8848</t>
+          <t>2053; 8675</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1618; 8212</t>
+          <t>2059; 9199</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8264; 18745</t>
+          <t>8713; 18760</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14814; 31105</t>
+          <t>13584; 30265</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2786; 9871</t>
+          <t>2708; 10348</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>609; 5738</t>
+          <t>603; 6747</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10721; 22897</t>
+          <t>10152; 22649</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>16134; 37918</t>
+          <t>15620; 37471</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6049; 15434</t>
+          <t>6184; 16008</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3363; 12071</t>
+          <t>3050; 11559</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21990; 37022</t>
+          <t>22266; 37819</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>34964; 61411</t>
+          <t>34459; 61423</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3588; 12711</t>
+          <t>3820; 13344</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3854; 13180</t>
+          <t>3802; 13102</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15979; 30691</t>
+          <t>16159; 30722</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24696; 41414</t>
+          <t>25186; 41391</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2780; 10947</t>
+          <t>2795; 10584</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5263; 15686</t>
+          <t>5575; 16599</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11874; 24347</t>
+          <t>11815; 24868</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>24435; 41531</t>
+          <t>24307; 42130</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8591; 20349</t>
+          <t>8696; 20900</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11525; 25716</t>
+          <t>11664; 25031</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>30839; 50479</t>
+          <t>32276; 51318</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>53781; 77446</t>
+          <t>53642; 78184</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>18261; 33783</t>
+          <t>18506; 34662</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>13779; 28946</t>
+          <t>13830; 27968</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>57080; 82128</t>
+          <t>56846; 81368</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>100387; 133507</t>
+          <t>100101; 131230</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>17678; 32695</t>
+          <t>17312; 32665</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16876; 32379</t>
+          <t>16690; 31697</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>59392; 85650</t>
+          <t>60081; 86057</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>132619; 173719</t>
+          <t>131763; 173549</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>39392; 61615</t>
+          <t>39819; 60805</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>34252; 56189</t>
+          <t>34508; 53864</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>123958; 159082</t>
+          <t>124700; 158533</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>242682; 295243</t>
+          <t>243120; 295973</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP19C02-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP19C02-Habitat-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4,32%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5,26%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>21,97%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>31,59%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>6,44%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>5,07%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>16,55%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>30,31%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4,32%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>5,26%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>21,97%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>31,71%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,73; 12,31</t>
+          <t>0,97; 8,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,92; 11,97</t>
+          <t>1,85; 10,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,92; 24,7</t>
+          <t>14,54; 31,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21,66; 39,87</t>
+          <t>20,35; 43,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,59; 8,98</t>
+          <t>2,8; 11,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,79; 11,56</t>
+          <t>1,86; 11,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,29; 31,19</t>
+          <t>9,78; 25,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,76; 39,0</t>
+          <t>22,62; 42,06</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,96; 8,66</t>
+          <t>2,84; 9,23</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,65; 8,98</t>
+          <t>2,71; 9,03</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14,6; 25,52</t>
+          <t>14,01; 25,67</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>21,76; 36,1</t>
+          <t>24,22; 39,97</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>7,84%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6,31%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>19,61%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>44,58%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>8,19%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>4,03%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>19,94%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>35,64%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>7,84%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>6,31%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>19,61%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>41,79%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,66; 12,93</t>
+          <t>4,23; 12,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,72; 7,77</t>
+          <t>3,45; 11,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,8; 25,86</t>
+          <t>13,48; 25,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28,18; 43,86</t>
+          <t>37,72; 51,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,25; 12,65</t>
+          <t>4,61; 12,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,41; 11,04</t>
+          <t>1,71; 7,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,64; 25,92</t>
+          <t>14,03; 26,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>36,08; 49,39</t>
+          <t>29,89; 45,46</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,32; 11,29</t>
+          <t>5,34; 10,93</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,94; 7,79</t>
+          <t>3,13; 7,91</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15,62; 24,53</t>
+          <t>15,63; 24,28</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>34,97; 44,98</t>
+          <t>36,88; 47,68</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>7,23%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2,74%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>21,08%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>22,4%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>6,38%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>5,96%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>17,23%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>20,02%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>7,23%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2,74%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>21,08%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>21,34%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,97; 12,54</t>
+          <t>3,73; 12,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,76; 12,35</t>
+          <t>0,76; 7,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,53; 24,82</t>
+          <t>13,84; 29,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,7; 28,3</t>
+          <t>14,55; 34,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,48; 13,29</t>
+          <t>2,71; 11,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,76; 8,46</t>
+          <t>2,44; 11,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,21; 29,47</t>
+          <t>10,94; 24,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,99; 31,16</t>
+          <t>13,35; 27,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,2; 10,88</t>
+          <t>4,17; 10,14</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,98; 7,49</t>
+          <t>2,17; 7,84</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14,61; 24,81</t>
+          <t>14,37; 24,68</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,17; 27,03</t>
+          <t>15,8; 28,44</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6,9%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10,2%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>16,66%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>30,64%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>7,75%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>8,24%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>20,78%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>32,86%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>6,9%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>10,2%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>16,66%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>32,64%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,98; 13,9</t>
+          <t>3,55; 12,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,09; 14,09</t>
+          <t>5,5; 16,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,82; 28,18</t>
+          <t>10,49; 23,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24,89; 40,91</t>
+          <t>23,08; 39,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,1; 11,75</t>
+          <t>3,89; 13,27</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,79; 17,24</t>
+          <t>4,04; 14,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,07; 23,29</t>
+          <t>14,77; 28,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>21,79; 37,76</t>
+          <t>27,11; 43,54</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,67; 11,23</t>
+          <t>4,72; 11,25</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,16; 13,22</t>
+          <t>6,11; 13,32</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14,96; 23,78</t>
+          <t>14,32; 23,34</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>25,21; 36,75</t>
+          <t>27,18; 38,7</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>6,67%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>6,34%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>19,55%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>33,71%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>7,34%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>5,76%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>18,97%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>29,71%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>6,67%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>6,34%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>19,55%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>32,62%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,27; 9,88</t>
+          <t>4,79; 9,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,92; 7,92</t>
+          <t>4,56; 8,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,68; 22,44</t>
+          <t>15,92; 23,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25,56; 33,51</t>
+          <t>29,28; 37,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,79; 9,03</t>
+          <t>5,47; 9,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,56; 8,66</t>
+          <t>4,02; 8,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,33; 23,38</t>
+          <t>15,77; 22,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>27,2; 35,82</t>
+          <t>26,78; 35,26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,59; 8,53</t>
+          <t>5,61; 8,89</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,8; 7,49</t>
+          <t>4,69; 7,74</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17,07; 21,7</t>
+          <t>16,83; 21,65</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>27,75; 33,78</t>
+          <t>29,68; 35,79</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>32</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>3551</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3960</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>16655</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>25736</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>4876</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>3744</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>11725</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>21148</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>3551</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>3960</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>16655</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>24369</t>
+          <t>23648</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>45518</t>
+          <t>49384</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2065; 9313</t>
+          <t>794; 7214</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1422; 8847</t>
+          <t>1392; 8086</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7030; 17498</t>
+          <t>11024; 23872</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15114; 27819</t>
+          <t>16575; 35141</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1303; 7377</t>
+          <t>2117; 9035</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1347; 8698</t>
+          <t>1376; 8405</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10833; 23644</t>
+          <t>6927; 18260</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14292; 33246</t>
+          <t>16803; 31240</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4677; 13678</t>
+          <t>4489; 14565</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3950; 13389</t>
+          <t>4038; 13467</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21409; 37425</t>
+          <t>20543; 37635</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>33735; 55965</t>
+          <t>37715; 62247</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>59</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>8747</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7241</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>21295</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>72367</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>9011</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>4511</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>21373</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>40532</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>8747</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>7241</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>21295</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>71298</t>
+          <t>44347</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>111830</t>
+          <t>116714</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5128; 14225</t>
+          <t>4726; 14105</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1923; 8691</t>
+          <t>3963; 13036</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14790; 27719</t>
+          <t>14642; 28204</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>32045; 49887</t>
+          <t>61237; 84285</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4740; 14126</t>
+          <t>5077; 14192</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3910; 12668</t>
+          <t>1908; 8884</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14815; 28151</t>
+          <t>15033; 28122</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>60383; 82659</t>
+          <t>34970; 53185</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11786; 25036</t>
+          <t>11847; 24237</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6666; 17638</t>
+          <t>7083; 17924</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33695; 52919</t>
+          <t>33727; 52393</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>98310; 126437</t>
+          <t>103004; 133171</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>28</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>5626</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2184</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>16200</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>25109</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>4418</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>4443</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>13026</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>21415</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>5626</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2184</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>16200</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>24783</t>
+          <t>20672</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>46198</t>
+          <t>45782</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2053; 8675</t>
+          <t>2908; 9756</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2059; 9199</t>
+          <t>609; 6108</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8713; 18760</t>
+          <t>10638; 22552</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13584; 30265</t>
+          <t>16314; 38545</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2708; 10348</t>
+          <t>1873; 7970</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>603; 6747</t>
+          <t>1818; 8724</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10152; 22649</t>
+          <t>8271; 18649</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>15620; 37471</t>
+          <t>13677; 28363</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6184; 16008</t>
+          <t>6134; 14907</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3050; 11559</t>
+          <t>3341; 12100</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>22266; 37819</t>
+          <t>21904; 37631</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>34459; 61423</t>
+          <t>33886; 61015</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>46</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>6217</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>9827</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>17789</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>32235</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>7436</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>7663</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>22654</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>33244</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>6217</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>9827</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>17789</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>32059</t>
+          <t>35590</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>65304</t>
+          <t>67824</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3820; 13344</t>
+          <t>3196; 11652</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3802; 13102</t>
+          <t>5296; 16031</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16159; 30722</t>
+          <t>11196; 25255</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>25186; 41391</t>
+          <t>24286; 41660</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2795; 10584</t>
+          <t>3731; 12742</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5575; 16599</t>
+          <t>3760; 13820</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11815; 24868</t>
+          <t>16105; 30599</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>24307; 42130</t>
+          <t>27812; 44661</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8696; 20900</t>
+          <t>8773; 20927</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11664; 25031</t>
+          <t>11561; 25214</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>32276; 51318</t>
+          <t>30898; 50360</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>53642; 78184</t>
+          <t>56472; 80406</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>165</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>24141</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>23211</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>71938</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>155447</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>25741</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>20361</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>68778</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>116339</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>24141</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>23211</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>71938</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>152510</t>
+          <t>124258</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>268849</t>
+          <t>279704</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>18506; 34662</t>
+          <t>17335; 33220</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>13830; 27968</t>
+          <t>16688; 32387</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>56846; 81368</t>
+          <t>58586; 84759</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>100101; 131230</t>
+          <t>135027; 174902</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>17312; 32665</t>
+          <t>19209; 34955</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16690; 31697</t>
+          <t>14207; 28582</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>60081; 86057</t>
+          <t>57202; 81714</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>131763; 173549</t>
+          <t>106109; 139724</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>39819; 60805</t>
+          <t>39954; 63354</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>34508; 53864</t>
+          <t>33764; 55641</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>124700; 158533</t>
+          <t>122953; 158157</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>243120; 295973</t>
+          <t>254485; 306859</t>
         </is>
       </c>
     </row>
